--- a/assets/constructions/examples/ctd_tge_module_holder.xlsx
+++ b/assets/constructions/examples/ctd_tge_module_holder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,41 +559,61 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VBMR075-00</t>
+          <t>WGCMER2525M50C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VG-Cut</t>
+          <t>WGC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VAR_VBM</t>
+          <t>WID_WMT-50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ISO_5610:19.05X19.05</t>
+          <t>ISO_5610:25X25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>VARGUS_VG_CUTR20</t>
+          <t>WIDIA_WMT-50R</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -610,31 +630,35 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>19.05</v>
+        <v>25</v>
       </c>
       <c r="P2" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7</v>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>114.3</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>150.25</v>
+      </c>
+      <c r="T2" t="n">
+        <v>125.25</v>
+      </c>
       <c r="U2" t="n">
-        <v>24.31</v>
+        <v>40</v>
       </c>
       <c r="V2" t="n">
-        <v>25</v>
+        <v>42.41</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
@@ -642,14 +666,20 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA Catalogue</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VBML075-90-C</t>
+          <t>VBML125-00-C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -674,16 +704,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ISO_5610:19.05X19.05</t>
+          <t>ISO_5610:31.75X31.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>VARGUS_VG_CUTR20</t>
+          <t>VARGUS_VG_CUT_HPCL</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -702,22 +732,22 @@
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>19.05</v>
+        <v>31.75</v>
       </c>
       <c r="P3" t="n">
-        <v>19.05</v>
+        <v>31.75</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>114.3</v>
+        <v>106.68</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>24.31</v>
+        <v>20.32</v>
       </c>
       <c r="V3" t="n">
-        <v>25</v>
+        <v>41.91</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
@@ -730,12 +760,26 @@
         <is>
           <t>2019 / Groovex Catalog</t>
         </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>322.13</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>29614.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VBMR125-00-C</t>
+          <t>VBMR075-90</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -760,16 +804,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ISO_5610:31.75X31.75</t>
+          <t>ISO_5610:19.05X19.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>VARGUS_VG_CUT_HPCR</t>
+          <t>VARGUS_VG_CUTL20</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -782,31 +826,31 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>31.75</v>
+        <v>19.05</v>
       </c>
       <c r="P4" t="n">
-        <v>31.75</v>
+        <v>19.05</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>106.68</v>
+        <v>114.3</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>20.32</v>
+        <v>24.31</v>
       </c>
       <c r="V4" t="n">
-        <v>41.91</v>
+        <v>25</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
@@ -816,42 +860,56 @@
         <is>
           <t>2019 / Groovex Catalog</t>
         </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>228.98</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>21050.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VBML075-00-C</t>
+          <t>WGCMSR3232P50C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VG-Cut</t>
+          <t>WGC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VAR_VBM</t>
+          <t>WID_WMT-50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ISO_5610:19.05X19.05</t>
+          <t>ISO_5610:32X32</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>VARGUS_VG_CUT_HPCL</t>
+          <t>WIDIA_WMT-50R</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -864,33 +922,33 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>19.05</v>
+        <v>32</v>
       </c>
       <c r="P5" t="n">
-        <v>19.05</v>
+        <v>32</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>81.28</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>158.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>133.616</v>
+      </c>
       <c r="U5" t="n">
-        <v>13.97</v>
-      </c>
-      <c r="V5" t="n">
-        <v>29.06</v>
-      </c>
+        <v>20.08</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="b">
         <v>1</v>
       </c>
@@ -900,44 +958,50 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA Catalogue</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WGCMSL2050C</t>
+          <t>VBML2525-90-C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WGC</t>
+          <t>VG-Cut</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WID_WMT-50</t>
+          <t>VAR_VBM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ISO_5610:31.75X31.75</t>
+          <t>ISO_5610:25X25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>WIDIA_WMT-50L</t>
+          <t>VARGUS_VG_CUT_HPCL</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -954,31 +1018,33 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>31.75</v>
+        <v>25</v>
       </c>
       <c r="P6" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>35</v>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>139.9</v>
+        <v>120</v>
       </c>
       <c r="T6" t="n">
-        <v>114.772</v>
-      </c>
-      <c r="U6" t="n">
-        <v>20.56</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
+        <v>102</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>25</v>
+      </c>
       <c r="W6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
@@ -986,8 +1052,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2017 / WIDIA Catalogue</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>310.23</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>28520.59</v>
       </c>
     </row>
   </sheetData>
